--- a/docs/VERB100_картинки_брифинг.xlsx
+++ b/docs/VERB100_картинки_брифинг.xlsx
@@ -11,7 +11,7 @@
     <sheet name="100 картинок" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'100 картинок'!$A$1:$I$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'100 картинок'!$A$1:$J$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +62,18 @@
       <color rgb="006E767B"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C8552C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0012A39A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +95,11 @@
         <fgColor rgb="00FBF7F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBF2F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -103,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -125,6 +140,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -145,6 +163,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -511,16 +532,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VERB 100 — брифинг на 100 картинок</t>
+          <t>VERB 100 — иллюстрации, версия 2</t>
         </is>
       </c>
     </row>
@@ -530,7 +551,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Что нужно: по одной картинке на каждый из 100 уроков. Лист «100 картинок» — вся таблица.</t>
+          <t>Стиль зафиксирован по вашей первой партии (уроки 17-20 и 65-76). Держимся его до конца курса.</t>
         </is>
       </c>
     </row>
@@ -540,124 +561,93 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>1. НАЗВАНИЕ ФАЙЛА — самое важное</t>
+          <t>1. ЧТО НУЖНО В ПЕРВУЮ ОЧЕРЕДЬ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Файл должен называться ровно так, как в колонке «Файл»: day-001.png, day-002.png … day-100.png.</t>
+          <t>Уроки 1-16. Это первые две недели занятий — они наступят раньше всего.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Приложение подхватывает картинки по имени. Любое другое имя — картинка не появится в уроке.</t>
+          <t>Уже сделано: 17-20 и 65-76 (16 из 100). Уроки 65-76 понадобятся только в ноябре.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Формат PNG или JPG, пропорции 16:9, минимум 1200×675 px. Больше — можно, меньше — размылится.</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2. ФОРМАТ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2. КАК ГЕНЕРИРОВАТЬ</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Сетка 2x2 с подписями подходит — я режу её сам и снимаю подписи. Просто скажите, какие номера в какой плитке.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>В генератор вставляете ДВЕ части подряд: сначала единый стиль (ниже), потом описание сцены из колонки «Промпт».</t>
+          <t>Если удобнее по одному файлу: day-001, day-002 … day-100, 3:2, минимум 1350x900, png или jpg.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Колонка «Готовый промпт» — это уже склеенные обе части. Просто копируете ячейку целиком.</t>
+          <t>Если генератор умеет — просите без номера в углу и без подписи: приложение рисует текст само.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Единый стиль обязателен для всех 100 — иначе приложение развалится визуально.</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>3. ЕДИНЫЙ СТИЛЬ (одинаковый для всех 100 картинок)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered.</t>
-        </is>
-      </c>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>3. ЕДИНЫЙ СТИЛЬ (вставлять перед описанием сцены)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="130" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>4. КОЛОНКА «ГОТОВЫЙ ПРОМПТ»</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>4. ПОРЯДОК РАБОТЫ</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>На листе «100 картинок» стиль и сцена уже склеены. Копируете ячейку целиком.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Не надо делать все 100 сразу. Делайте партиями по 10 — как раз на 10 дней занятий вперёд.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Партия 1: day-001 … day-010. Присылаете — я вставляю в уроки. Дальше по мере прохождения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>5. ЕСЛИ СЦЕНА НЕ НРАВИТСЯ</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Колонка «Что на картинке» — моё предложение, не приказ. Меняйте свободно, главное — сохранить стиль и имя файла.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Картинка должна помогать вспомнить ФРАЗУ, а не просто иллюстрировать глагол.</t>
+          <t>Колонка «Статус» показывает, что уже в приложении.</t>
         </is>
       </c>
     </row>
@@ -672,18 +662,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="95" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="92" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -704,32 +695,37 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
           <t>Файл</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Предложение (EN)</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Перевод (RU)</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>한국어</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Что на картинке</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Готовый промпт (копировать целиком)</t>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Готовый промпт</t>
         </is>
       </c>
     </row>
@@ -747,75 +743,85 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>day-001.png</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>day-001</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Do you have any pets?</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>У тебя есть домашние животные?</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>반려동물 키워요?</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>Двое на диване, на коленях у одного золотистый ретривер</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: two friends chatting on a sofa, a golden retriever resting its head on one lap, cozy living room</t>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: two friends chatting on a sofa, a golden retriever resting its head on one lap, cozy living room</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>HAVE ②</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>day-002.png</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>day-002</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>I just had a snack, so I'm not that hungry.</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Я только что перекусил, так что не особо голоден.</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>방금 간식 먹어서 별로 안 배고파요.</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>Человек отодвигает тарелку, рядом пустая обёртка от батончика</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person politely pushing a plate away at a table, an empty snack wrapper beside them, small gesture of refusal</t>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person politely pushing a plate away at a table, an empty snack wrapper beside them, small gesture of refusal</t>
         </is>
       </c>
     </row>
@@ -833,75 +839,85 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>day-003.png</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>day-003</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>I had a weird morning yesterday.</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>У меня вчера было странное утро.</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>어제 아침이 좀 이상했어요.</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Человек с кофе смотрит в окно, за окном что-то нелепое — птица на самокате</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person holding coffee by a window, looking puzzled at something odd outside, morning light</t>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person holding coffee by a window, looking puzzled at something odd outside, morning light</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>HAVE ④</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>day-004.png</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>day-004</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Samsung is having a new-product launch today.</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Samsung сегодня проводит презентацию нового продукта.</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>삼성이 오늘 신제품 발표회를 열어요.</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Сцена презентации: большой экран, спикер, зал</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a tech product launch stage, large screen, presenter in front of a seated audience, spotlights</t>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a tech product launch stage, large screen, presenter in front of a seated audience, spotlights</t>
         </is>
       </c>
     </row>
@@ -919,75 +935,85 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>day-005.png</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>day-005</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>I have some chores to do in the afternoon.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>У меня после обеда есть кое-какие дела по дому.</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>오후에 집안일이 좀 있어요.</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Список дел на холодильнике, корзина с бельём, губка и швабра</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a fridge door with a to-do list magnet, laundry basket and mop nearby, sunny apartment</t>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a fridge door with a to-do list magnet, laundry basket and mop nearby, sunny apartment</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>HAVE ⑥</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>day-006.png</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>day-006</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>The Gion district in Kyoto has a charming vibe.</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>У квартала Гион в Киото особое очарование.</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>교토 기온 거리는 분위기가 참 좋아요.</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>Узкая улочка Гион: деревянные дома, красные фонари, вечер</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a narrow traditional Kyoto street at dusk, wooden machiya houses, warm red lanterns</t>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a narrow traditional Kyoto street at dusk, wooden machiya houses, warm red lanterns</t>
         </is>
       </c>
     </row>
@@ -1005,75 +1031,85 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>day-007.png</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>day-007</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>Thank you for having us over for dinner.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Спасибо, что пригласили нас на ужин.</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>저녁 식사에 초대해 주셔서 감사합니다.</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Хозяева провожают гостей у двери, гости благодарят</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: hosts saying goodbye to guests at a front door after dinner, warm hallway light, handshake</t>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: hosts saying goodbye to guests at a front door after dinner, warm hallway light, handshake</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>HAVE ⑧</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>day-008.png</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>day-008</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>You could have Daniel give you a ride.</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Ты можешь попросить Даниэля тебя подвезти.</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>다니엘한테 태워 달라고 하면 되잖아요.</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Один человек указывает на друга у машины, тот открывает пассажирскую дверь</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: one person gesturing toward a friend beside a car who is opening the passenger door, street at dusk</t>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: one person gesturing toward a friend beside a car who is opening the passenger door, street at dusk</t>
         </is>
       </c>
     </row>
@@ -1091,75 +1127,85 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>day-009.png</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>day-009</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>My boyfriend got a ticket to the concert.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Мой парень достал билет на концерт.</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>남자친구가 콘서트 티켓을 구했어요.</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Рука держит билет на концерт, на фоне светящаяся сцена</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a hand holding a concert ticket, glowing stage and crowd blurred in the background</t>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a hand holding a concert ticket, glowing stage and crowd blurred in the background</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>GET ②</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>day-010.png</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>day-010</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>You have to book way in advance to get a table there.</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>Столик там надо бронировать сильно заранее.</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>거기는 한참 전에 예약해야 자리가 있어요.</t>
         </is>
       </c>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Телефон с экраном бронирования, все даты заняты, на фоне популярный ресторан</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a phone showing a restaurant booking screen with all dates greyed out, busy restaurant behind</t>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a phone showing a restaurant booking screen with all dates greyed out, busy restaurant behind</t>
         </is>
       </c>
     </row>
@@ -1177,75 +1223,85 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>day-011.png</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>day-011</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>Let's get a drink after work.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Давай после работы выпьем по бокалу.</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>퇴근하고 한잔하죠.</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Двое коллег с пиджаками на руке идут в бар вечером</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: two colleagues with jackets over their arms walking into a bar in the evening, neon sign</t>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: two colleagues with jackets over their arms walking into a bar in the evening, neon sign</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>GET ④</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>day-012.png</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>day-012</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>Can I get a large Americano?</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Можно мне большой американо?</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>아메리카노 큰 걸로 주세요.</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>Клиент у стойки кофейни, бариста готовит большой стакан</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a customer ordering at a coffee shop counter, barista preparing a large iced americano</t>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a customer ordering at a coffee shop counter, barista preparing a large iced americano</t>
         </is>
       </c>
     </row>
@@ -1263,75 +1319,85 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>day-013.png</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>day-013</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>We just got back last night.</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Мы только вчера вечером вернулись.</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>저희 어젯밤에 막 돌아왔어요.</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Пара заходит домой с чемоданами поздно вечером</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a couple entering their apartment at night with suitcases, hallway light on, tired but happy</t>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a couple entering their apartment at night with suitcases, hallway light on, tired but happy</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>GET ⑥</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>day-014.png</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>day-014</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>I don't get why she's so upset.</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>Я не понимаю, почему она так расстроена.</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>걔가 왜 그렇게 속상해하는지 모르겠어요.</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>Человек с растерянным жестом, на фоне другой отвернулся</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a confused person shrugging, another figure turned away in the background, tense mood</t>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a confused person shrugging, another figure turned away in the background, tense mood</t>
         </is>
       </c>
     </row>
@@ -1349,75 +1415,85 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>day-015.png</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>day-015</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>I feel like my English is getting rusty.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Чувствую, что мой английский начинает ржаветь.</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>영어가 점점 녹스는 것 같아요.</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Раскрытый учебник английского в пыли, рядом чашка</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a dusty open English textbook on a desk with a mug, faint rust-colored tint, neglected study corner</t>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a dusty open English textbook on a desk with a mug, faint rust-colored tint, neglected study corner</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>GET ⑧</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>day-016.png</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>day-016</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>I get a headache if I don't drink coffee.</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>Если я не выпью кофе, у меня болит голова.</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>커피를 안 마시면 머리가 아파요.</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>Человек трёт виски, рядом нетронутая чашка кофе</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person rubbing their temples at a desk, an untouched coffee cup beside them, morning office</t>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person rubbing their temples at a desk, an untouched coffee cup beside them, morning office</t>
         </is>
       </c>
     </row>
@@ -1433,77 +1509,87 @@
           <t>GET ⑨</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>day-017.png</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>day-017</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>I need to get these groceries home.</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Мне нужно довезти эти продукты до дома.</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>이 장 본 것들 집까지 가져가야 해요.</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Человек с двумя тяжёлыми пакетами продуктов на улице</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person carrying two heavy grocery bags along a sidewalk, slightly struggling</t>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person carrying two heavy grocery bags along a sidewalk, slightly struggling</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>GET ⑩</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>day-018.png</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>day-018</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>This area doesn't get much sunshine.</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>В этом районе мало солнца.</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>이 동네는 햇빛이 잘 안 들어요.</t>
         </is>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>Тенистый двор между высокими домами, узкая полоска света</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a shaded courtyard between tall buildings, one thin strip of sunlight on the ground</t>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a shaded courtyard between tall buildings, one thin strip of sunlight on the ground</t>
         </is>
       </c>
     </row>
@@ -1519,77 +1605,87 @@
           <t>GET ⑪</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>day-019.png</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>day-019</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>We got you a spot next to us.</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Мы заняли тебе место рядом с нами.</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>우리 옆에 자리 맡아 놨어요.</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>Люди в зале, на соседнем кресле лежит куртка — место занято</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: people seated in an auditorium, a jacket saving an empty seat beside them, someone waving</t>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: people seated in an auditorium, a jacket saving an empty seat beside them, someone waving</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>GET ⑫</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>day-020.png</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>day-020</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>I got my hair dyed yesterday.</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>Я вчера покрасил волосы.</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>어제 머리 염색했어요.</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>Клиент в кресле парикмахерской, мастер показывает результат в зеркале</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a client in a salon chair admiring newly dyed hair in the mirror, stylist behind them</t>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a client in a salon chair admiring newly dyed hair in the mirror, stylist behind them</t>
         </is>
       </c>
     </row>
@@ -1605,77 +1701,79 @@
           <t>GET ⑬</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>day-021.png</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>day-021</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>How can I get my kids to eat vegetables?</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>Как заставить детей есть овощи?</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>애들이 채소를 먹게 하려면 어떻게 해야 하죠?</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Ребёнок отодвигает брокколи, родитель уговаривает</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a child pushing broccoli to the edge of the plate while a parent gently coaxes, kitchen table</t>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a child pushing broccoli to the edge of the plate while a parent gently coaxes, kitchen table</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>MAKE ①</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>day-022.png</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr"/>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>day-022</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>I can make you steamed galbi, if you want.</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>Могу приготовить тебе тушёные кальби, если хочешь.</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>원하면 갈비찜 해 줄게요.</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>Домашняя кухня, кастрюля кальби-ччим, хозяин показывает блюдо</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a home cook lifting the lid off a pot of Korean braised short ribs, steam rising, family kitchen</t>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a home cook lifting the lid off a pot of Korean braised short ribs, steam rising, family kitchen</t>
         </is>
       </c>
     </row>
@@ -1691,77 +1789,79 @@
           <t>MAKE ②</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>day-023.png</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>day-023</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Having children has made me a better husband.</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Дети сделали меня лучшим мужем.</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>아이가 생기면서 더 좋은 남편이 됐어요.</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Отец с ребёнком на руках моет посуду, жена рядом улыбается</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a father holding a toddler in one arm while doing dishes, partner smiling nearby, warm kitchen</t>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a father holding a toddler in one arm while doing dishes, partner smiling nearby, warm kitchen</t>
         </is>
       </c>
     </row>
     <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>MAKE ③</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>day-024.png</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr"/>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>day-024</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>I made myself go to the gym today.</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>Я заставил себя сегодня пойти в зал.</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>오늘 억지로 헬스장에 갔어요.</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
         <is>
           <t>Человек с усилием завязывает кроссовки у двери спортзала</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person reluctantly tying running shoes at a gym entrance, gym equipment behind</t>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person reluctantly tying running shoes at a gym entrance, gym equipment behind</t>
         </is>
       </c>
     </row>
@@ -1777,77 +1877,79 @@
           <t>MAKE ④</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>day-025.png</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr"/>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>day-025</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>Sitting in traffic makes me feel anxious.</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Стоять в пробке меня нервирует.</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>차 막히면 불안해져요.</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Водитель в пробке, руки на руле, бесконечные стоп-огни</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a driver gripping the wheel in heavy traffic, endless red tail lights ahead, tense expression</t>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a driver gripping the wheel in heavy traffic, endless red tail lights ahead, tense expression</t>
         </is>
       </c>
     </row>
     <row r="27" ht="44" customHeight="1">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>MAKE ⑤</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>day-026.png</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr"/>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>day-026</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>They made it to the finals.</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>Они вышли в финал.</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>걔네 결승에 올라갔어요.</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>Команда празднует на поле, табло с надписью FINAL</t>
         </is>
       </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a sports team celebrating on the field, stadium scoreboard reading FINAL, confetti</t>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a sports team celebrating on the field, stadium scoreboard reading FINAL, confetti</t>
         </is>
       </c>
     </row>
@@ -1863,77 +1965,79 @@
           <t>MAKE ⑥</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>day-027.png</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>day-027</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>Those two would make a great couple.</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Эти двое отлично смотрелись бы вместе.</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>저 둘 잘 어울릴 것 같은데요.</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>Двое друзей наблюдают за парой издалека и переглядываются</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: two friends at a cafe glancing knowingly at a man and woman talking across the room</t>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: two friends at a cafe glancing knowingly at a man and woman talking across the room</t>
         </is>
       </c>
     </row>
     <row r="29" ht="44" customHeight="1">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>TAKE ①</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>day-028.png</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr"/>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>day-028</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>If we can't finish, we can take the leftovers home.</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>Если не доедим, можем забрать остатки домой.</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>다 못 먹으면 남은 거 싸 가면 돼요.</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>Официант упаковывает остатки в контейнер</t>
         </is>
       </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a server packing leftover food into a takeout box at a restaurant table</t>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a server packing leftover food into a takeout box at a restaurant table</t>
         </is>
       </c>
     </row>
@@ -1949,77 +2053,79 @@
           <t>TAKE ②</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>day-029.png</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>day-029</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>That kindergarten doesn't take kids under five.</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Этот детский сад не берёт детей младше пяти.</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>그 유치원은 다섯 살 미만은 안 받아요.</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>Вход в детский сад, табличка с возрастом, родитель с малышом</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a kindergarten entrance with an age policy sign, a parent holding a small child outside</t>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a kindergarten entrance with an age policy sign, a parent holding a small child outside</t>
         </is>
       </c>
     </row>
     <row r="31" ht="44" customHeight="1">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>TAKE ③</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>day-030.png</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr"/>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>day-030</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>Kevin doesn't take advice from anyone.</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>Кевин ни от кого не принимает советов.</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>케빈은 누구 말도 안 들어요.</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>Человек скрестил руки и отвернулся, коллега что-то объясняет</t>
         </is>
       </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a man with crossed arms looking away while a colleague tries to advise him, office</t>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a man with crossed arms looking away while a colleague tries to advise him, office</t>
         </is>
       </c>
     </row>
@@ -2035,77 +2141,79 @@
           <t>TAKE ④</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>day-031.png</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>day-031</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>It takes a lot to make me angry.</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>Меня трудно вывести из себя.</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>저는 웬만해선 화 안 내요.</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Человек спокойно улыбается посреди хаоса в офисе</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a calm person smiling amid chaotic office commotion, papers flying, unbothered</t>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a calm person smiling amid chaotic office commotion, papers flying, unbothered</t>
         </is>
       </c>
     </row>
     <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>TAKE ⑤</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t>day-032.png</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr"/>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>day-032</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>It took me months to finish reading that book.</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>Я читал эту книгу несколько месяцев.</t>
         </is>
       </c>
-      <c r="G33" s="13" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>그 책 다 읽는 데 몇 달 걸렸어요.</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="I33" s="14" t="inlineStr">
         <is>
           <t>Толстая книга с закладкой почти в конце, календарь на стене</t>
         </is>
       </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a thick book with a bookmark near the end on a desk, wall calendar with many crossed days</t>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a thick book with a bookmark near the end on a desk, wall calendar with many crossed days</t>
         </is>
       </c>
     </row>
@@ -2121,77 +2229,79 @@
           <t>TAKE ⑥</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>day-033.png</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>day-033</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>She didn't take it well.</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>Она восприняла это тяжело.</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>걔는 그걸 많이 힘들어했어요.</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Человек сидит один на скамейке, подперев голову</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person sitting alone on a park bench, head in hands, overcast evening</t>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person sitting alone on a park bench, head in hands, overcast evening</t>
         </is>
       </c>
     </row>
     <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>day-034.png</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr"/>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>day-034</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>I do a lot of admin work at my job.</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>На работе у меня много бумажной работы.</t>
         </is>
       </c>
-      <c r="G35" s="13" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>회사에서 행정 업무를 많이 해요.</t>
         </is>
       </c>
-      <c r="H35" s="13" t="inlineStr">
+      <c r="I35" s="14" t="inlineStr">
         <is>
           <t>Офисный стол, стопки документов, человек ставит подписи</t>
         </is>
       </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: an office desk piled with paperwork, a person signing forms, stamp and folders</t>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: an office desk piled with paperwork, a person signing forms, stamp and folders</t>
         </is>
       </c>
     </row>
@@ -2207,77 +2317,79 @@
           <t>LIKE</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>day-035.png</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr"/>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>day-035</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>I don't like to play golf, but I have to for my job.</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Я не люблю играть в гольф, но приходится по работе.</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>골프 좋아하진 않는데 일 때문에 쳐요.</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>Мужчина в деловой одежде с клюшкой, без энтузиазма</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a businessman on a golf course holding a club with a resigned expression, colleagues behind</t>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a businessman on a golf course holding a club with a resigned expression, colleagues behind</t>
         </is>
       </c>
     </row>
     <row r="37" ht="44" customHeight="1">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>SEE</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>day-036.png</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr"/>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>day-036</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>I haven't seen you for a while.</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>Давно тебя не видел.</t>
         </is>
       </c>
-      <c r="G37" s="13" t="inlineStr">
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>오랜만이에요.</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
+      <c r="I37" s="14" t="inlineStr">
         <is>
           <t>Двое обнимаются при встрече на улице</t>
         </is>
       </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: two friends hugging in greeting on a city street, genuine smiles, reunion</t>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: two friends hugging in greeting on a city street, genuine smiles, reunion</t>
         </is>
       </c>
     </row>
@@ -2293,77 +2405,79 @@
           <t>KNOW</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>day-037.png</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr"/>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>day-037</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>I know the owner.</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>Я знаком с владельцем.</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>제가 사장님이랑 아는 사이예요.</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>Гость приветствует владельца ресторана за руку</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a guest shaking hands warmly with a restaurant owner near the counter</t>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a guest shaking hands warmly with a restaurant owner near the counter</t>
         </is>
       </c>
     </row>
     <row r="39" ht="44" customHeight="1">
-      <c r="A39" s="11" t="n">
+      <c r="A39" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>WORK ①</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>day-038.png</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr"/>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>day-038</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>This diet really worked for me.</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>Эта диета мне реально помогла.</t>
         </is>
       </c>
-      <c r="G39" s="13" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>이 다이어트 저한테 진짜 효과 있었어요.</t>
         </is>
       </c>
-      <c r="H39" s="13" t="inlineStr">
+      <c r="I39" s="14" t="inlineStr">
         <is>
           <t>Человек застёгивает свободные джинсы, на стене фото «до»</t>
         </is>
       </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person holding out the loose waistband of their jeans, before-photo on the wall</t>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person holding out the loose waistband of their jeans, before-photo on the wall</t>
         </is>
       </c>
     </row>
@@ -2379,77 +2493,79 @@
           <t>WORK ②</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>day-039.png</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr"/>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>day-039</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>Dating doesn't work that way anymore. Times have changed.</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>Свидания теперь устроены иначе. Времена изменились.</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>요즘 연애는 그런 식이 아니에요. 시대가 변했죠.</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>Слева пара со свиданием вслепую в старом стиле, справа — приложение знакомств</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a split scene: an old-fashioned blind date at a cafe versus someone swiping on a dating app</t>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a split scene: an old-fashioned blind date at a cafe versus someone swiping on a dating app</t>
         </is>
       </c>
     </row>
     <row r="41" ht="44" customHeight="1">
-      <c r="A41" s="11" t="n">
+      <c r="A41" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>GO ①</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>day-040.png</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr"/>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>day-040</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>I'm glad to hear your trip went well.</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>Рад слышать, что поездка прошла хорошо.</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>여행 잘 다녀오셨다니 다행이에요.</t>
         </is>
       </c>
-      <c r="H41" s="13" t="inlineStr">
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>Друзья смотрят фото из поездки на телефоне</t>
         </is>
       </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: two friends looking at travel photos on a phone, one just back from a trip, suitcase nearby</t>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: two friends looking at travel photos on a phone, one just back from a trip, suitcase nearby</t>
         </is>
       </c>
     </row>
@@ -2465,77 +2581,79 @@
           <t>GO ②</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>day-041.png</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr"/>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>day-041</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>The screen went dark for some reason.</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>Экран почему-то погас.</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>화면이 갑자기 꺼졌어요.</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>Человек смотрит на потухший экран ноутбука</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person staring at a laptop with a completely black screen, puzzled, desk lamp on</t>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person staring at a laptop with a completely black screen, puzzled, desk lamp on</t>
         </is>
       </c>
     </row>
     <row r="43" ht="44" customHeight="1">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>GO ③</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>day-042.png</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr"/>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>day-042</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>Food trash goes in this yellow bag.</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>Пищевые отходы — в этот жёлтый пакет.</t>
         </is>
       </c>
-      <c r="G43" s="13" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
         <is>
           <t>음식물 쓰레기는 이 노란 봉투에 넣으면 돼요.</t>
         </is>
       </c>
-      <c r="H43" s="13" t="inlineStr">
+      <c r="I43" s="14" t="inlineStr">
         <is>
           <t>Кухня, жёлтый пакет для пищевых отходов, человек показывает</t>
         </is>
       </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a kitchen with a yellow food-waste bag, one person pointing it out to another, Korean apartment</t>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a kitchen with a yellow food-waste bag, one person pointing it out to another, Korean apartment</t>
         </is>
       </c>
     </row>
@@ -2551,77 +2669,79 @@
           <t>WANT</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>day-043.png</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr"/>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>day-043</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>Do you want a ride to the station?</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>Подвезти тебя до вокзала?</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>역까지 태워다 줄까요?</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>Водитель открывает пассажирскую дверь, вдали вокзал</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a driver leaning over to open the passenger door, train station visible down the street</t>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a driver leaning over to open the passenger door, train station visible down the street</t>
         </is>
       </c>
     </row>
     <row r="45" ht="44" customHeight="1">
-      <c r="A45" s="11" t="n">
+      <c r="A45" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>SAY</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>day-044.png</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr"/>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>day-044</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>The website says the item is out of stock.</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>На сайте написано, что товара нет в наличии.</t>
         </is>
       </c>
-      <c r="G45" s="13" t="inlineStr">
+      <c r="H45" s="14" t="inlineStr">
         <is>
           <t>사이트에 품절이라고 나와 있어요.</t>
         </is>
       </c>
-      <c r="H45" s="13" t="inlineStr">
+      <c r="I45" s="14" t="inlineStr">
         <is>
           <t>Экран телефона: OUT OF STOCK</t>
         </is>
       </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a phone screen showing OUT OF STOCK on a shopping site, disappointed person holding it</t>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a phone screen showing OUT OF STOCK on a shopping site, disappointed person holding it</t>
         </is>
       </c>
     </row>
@@ -2637,77 +2757,79 @@
           <t>LET ①</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>day-045.png</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr"/>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>day-045</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>Let me walk you out.</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>Давай я тебя провожу.</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>제가 배웅해 드릴게요.</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Хозяин провожает гостя до лифта</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a host walking a guest toward the elevator, gesturing politely, office corridor</t>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a host walking a guest toward the elevator, gesturing politely, office corridor</t>
         </is>
       </c>
     </row>
     <row r="47" ht="44" customHeight="1">
-      <c r="A47" s="11" t="n">
+      <c r="A47" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="13" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>LET ②</t>
         </is>
       </c>
-      <c r="D47" s="14" t="inlineStr">
-        <is>
-          <t>day-046.png</t>
-        </is>
-      </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr"/>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>day-046</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>Could you let me finish my sentence, please?</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>Дайте мне, пожалуйста, договорить.</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr">
         <is>
           <t>제 말 좀 끝까지 들어 주시겠어요?</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
+      <c r="I47" s="14" t="inlineStr">
         <is>
           <t>Человек поднимает ладонь, прося не перебивать, на совещании</t>
         </is>
       </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person raising an open palm asking not to be interrupted during a meeting</t>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person raising an open palm asking not to be interrupted during a meeting</t>
         </is>
       </c>
     </row>
@@ -2723,77 +2845,79 @@
           <t>LET ③</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>day-047.png</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr"/>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>day-047</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>I can't let nasty comments discourage me.</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>Не могу позволить злым комментариям меня сломить.</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>악플 때문에 위축되지 않으려고요.</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>Человек закрывает ноутбук с комментариями и выпрямляется</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person closing a laptop full of negative comments and sitting up straight, resolute</t>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person closing a laptop full of negative comments and sitting up straight, resolute</t>
         </is>
       </c>
     </row>
     <row r="49" ht="44" customHeight="1">
-      <c r="A49" s="11" t="n">
+      <c r="A49" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>GIVE ①</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
-        <is>
-          <t>day-048.png</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr"/>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>day-048</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>This song gives me chills.</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>От этой песни у меня мурашки.</t>
         </is>
       </c>
-      <c r="G49" s="13" t="inlineStr">
+      <c r="H49" s="14" t="inlineStr">
         <is>
           <t>이 노래 들으면 소름 돋아요.</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="I49" s="14" t="inlineStr">
         <is>
           <t>Человек в наушниках с закрытыми глазами, мурашки на руке</t>
         </is>
       </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person with eyes closed wearing headphones, goosebumps on their forearm, moved by music</t>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person with eyes closed wearing headphones, goosebumps on their forearm, moved by music</t>
         </is>
       </c>
     </row>
@@ -2809,77 +2933,79 @@
           <t>GIVE ②</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>day-049.png</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr"/>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>day-049</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>Let me give you a quick update on the project.</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Коротко расскажу, как идёт проект.</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>프로젝트 진행 상황 간단히 말씀드릴게요.</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>Совещание, спикер у экрана с графиком проекта</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a short stand-up meeting, one person presenting a project timeline on a screen</t>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a short stand-up meeting, one person presenting a project timeline on a screen</t>
         </is>
       </c>
     </row>
     <row r="51" ht="44" customHeight="1">
-      <c r="A51" s="11" t="n">
+      <c r="A51" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>KEEP ①</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
-        <is>
-          <t>day-050.png</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr"/>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>day-050</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
         <is>
           <t>You can keep the omelet pan.</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="G51" s="14" t="inlineStr">
         <is>
           <t>Сковородку для омлета можешь оставить себе.</t>
         </is>
       </c>
-      <c r="G51" s="13" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
         <is>
           <t>그 오믈렛 팬은 그냥 가지세요.</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
+      <c r="I51" s="14" t="inlineStr">
         <is>
           <t>Один протягивает другому сковородку, жест «оставь себе»</t>
         </is>
       </c>
-      <c r="I51" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: one person handing an omelet pan to another with a keep-it gesture, kitchen doorway</t>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: one person handing an omelet pan to another with a keep-it gesture, kitchen doorway</t>
         </is>
       </c>
     </row>
@@ -2895,77 +3021,79 @@
           <t>KEEP ②</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>day-051.png</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr"/>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>day-051</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>This website keeps giving me an error message.</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Этот сайт постоянно выдаёт мне ошибку.</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>이 사이트 자꾸 오류가 떠요.</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>Экран с сообщением об ошибке, человек раздражён</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a laptop screen showing a repeated error message, frustrated person clicking again</t>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a laptop screen showing a repeated error message, frustrated person clicking again</t>
         </is>
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C53" s="13" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>KEEP ③</t>
         </is>
       </c>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>day-052.png</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr"/>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>day-052</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
         <is>
           <t>Wow, how do you keep your bathroom so clean?</t>
         </is>
       </c>
-      <c r="F53" s="13" t="inlineStr">
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>Как ты держишь ванную в такой чистоте?</t>
         </is>
       </c>
-      <c r="G53" s="13" t="inlineStr">
+      <c r="H53" s="14" t="inlineStr">
         <is>
           <t>화장실을 어떻게 이렇게 깨끗하게 유지해요?</t>
         </is>
       </c>
-      <c r="H53" s="13" t="inlineStr">
+      <c r="I53" s="14" t="inlineStr">
         <is>
           <t>Сверкающая чистая ванная, гость удивлён</t>
         </is>
       </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a spotless sparkling bathroom, a guest peeking in looking impressed</t>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a spotless sparkling bathroom, a guest peeking in looking impressed</t>
         </is>
       </c>
     </row>
@@ -2981,77 +3109,79 @@
           <t>LEAVE ①</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>day-053.png</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr"/>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>day-053</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>I'm leaving on the first flight out tomorrow.</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>Я улетаю завтра первым рейсом.</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>내일 첫 비행기로 떠나요.</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>Человек с чемоданом в пустом аэропорту на рассвете</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a traveler with a suitcase in an empty airport terminal at dawn, departure board glowing</t>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a traveler with a suitcase in an empty airport terminal at dawn, departure board glowing</t>
         </is>
       </c>
     </row>
     <row r="55" ht="44" customHeight="1">
-      <c r="A55" s="11" t="n">
+      <c r="A55" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="12" t="n">
+      <c r="B55" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>LEAVE ②</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>day-054.png</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr"/>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>day-054</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>I left you some pizza over there if you're hungry.</t>
         </is>
       </c>
-      <c r="F55" s="13" t="inlineStr">
+      <c r="G55" s="14" t="inlineStr">
         <is>
           <t>Я оставил тебе там пиццу, если проголодаешься.</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="H55" s="14" t="inlineStr">
         <is>
           <t>배고프면 저기 피자 좀 남겨 놨어요.</t>
         </is>
       </c>
-      <c r="H55" s="13" t="inlineStr">
+      <c r="I55" s="14" t="inlineStr">
         <is>
           <t>Кусок пиццы на столе под фольгой с запиской</t>
         </is>
       </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a couple of pizza slices left on a kitchen counter with a sticky note, late evening</t>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a couple of pizza slices left on a kitchen counter with a sticky note, late evening</t>
         </is>
       </c>
     </row>
@@ -3067,77 +3197,79 @@
           <t>LEAVE ③</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>day-055.png</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr"/>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>day-055</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>Do you want me to leave the door open?</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Оставить дверь открытой?</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>문 열어 둘까요?</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>Человек держит дверь приоткрытой и оглядывается</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person holding a door half open, looking back over their shoulder questioningly</t>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person holding a door half open, looking back over their shoulder questioningly</t>
         </is>
       </c>
     </row>
     <row r="57" ht="44" customHeight="1">
-      <c r="A57" s="11" t="n">
+      <c r="A57" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="12" t="n">
+      <c r="B57" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>BRING</t>
         </is>
       </c>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>day-056.png</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr"/>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>day-056</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
         <is>
           <t>Do you mind if I bring Nick with me?</t>
         </is>
       </c>
-      <c r="F57" s="13" t="inlineStr">
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>Ничего, если я приведу с собой Ника?</t>
         </is>
       </c>
-      <c r="G57" s="13" t="inlineStr">
+      <c r="H57" s="14" t="inlineStr">
         <is>
           <t>닉도 같이 데려가도 될까요?</t>
         </is>
       </c>
-      <c r="H57" s="13" t="inlineStr">
+      <c r="I57" s="14" t="inlineStr">
         <is>
           <t>Человек пишет сообщение, рядом стоит друг</t>
         </is>
       </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person texting while a friend waits beside them, both ready to go out</t>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person texting while a friend waits beside them, both ready to go out</t>
         </is>
       </c>
     </row>
@@ -3153,77 +3285,79 @@
           <t>HEAD</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>day-057.png</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr"/>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>day-057</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>I'm heading down to Busan this weekend.</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>На выходных еду в Пусан.</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>이번 주말에 부산 내려가요.</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>Скоростной поезд KTX, вдалеке море Пусана</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a KTX high-speed train departing, Busan coastline in the distance, weekend trip mood</t>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a KTX high-speed train departing, Busan coastline in the distance, weekend trip mood</t>
         </is>
       </c>
     </row>
     <row r="59" ht="44" customHeight="1">
-      <c r="A59" s="11" t="n">
+      <c r="A59" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="12" t="n">
+      <c r="B59" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>COME</t>
         </is>
       </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>day-058.png</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr"/>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>day-058</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
         <is>
           <t>Are you coming with us to the party?</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr">
+      <c r="G59" s="14" t="inlineStr">
         <is>
           <t>Ты с нами на вечеринку?</t>
         </is>
       </c>
-      <c r="G59" s="13" t="inlineStr">
+      <c r="H59" s="14" t="inlineStr">
         <is>
           <t>우리랑 파티 갈래요?</t>
         </is>
       </c>
-      <c r="H59" s="13" t="inlineStr">
+      <c r="I59" s="14" t="inlineStr">
         <is>
           <t>Друзья зовут кого-то рукой, вечеринка позади</t>
         </is>
       </c>
-      <c r="I59" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: friends waving someone over to join them, party lights in the background</t>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: friends waving someone over to join them, party lights in the background</t>
         </is>
       </c>
     </row>
@@ -3239,77 +3373,79 @@
           <t>PUT ①</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>day-059.png</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr"/>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>day-059</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>They put me on the waiting list.</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Меня поставили в лист ожидания.</t>
         </is>
       </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>저 대기자 명단에 올려놨대요.</t>
         </is>
       </c>
-      <c r="H60" s="8" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>Экран с надписью WAITING LIST, человек ждёт</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a screen or clipboard reading WAITING LIST, a person waiting in a lobby chair</t>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a screen or clipboard reading WAITING LIST, a person waiting in a lobby chair</t>
         </is>
       </c>
     </row>
     <row r="61" ht="44" customHeight="1">
-      <c r="A61" s="11" t="n">
+      <c r="A61" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="12" t="n">
+      <c r="B61" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C61" s="14" t="inlineStr">
         <is>
           <t>PUT ②</t>
         </is>
       </c>
-      <c r="D61" s="14" t="inlineStr">
-        <is>
-          <t>day-060.png</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr"/>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>day-060</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
         <is>
           <t>Nasty comments always put me in a bad mood.</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="G61" s="14" t="inlineStr">
         <is>
           <t>Злые комментарии всегда портят мне настроение.</t>
         </is>
       </c>
-      <c r="G61" s="13" t="inlineStr">
+      <c r="H61" s="14" t="inlineStr">
         <is>
           <t>악플 보면 항상 기분이 상해요.</t>
         </is>
       </c>
-      <c r="H61" s="13" t="inlineStr">
+      <c r="I61" s="14" t="inlineStr">
         <is>
           <t>Человек хмурится, глядя в телефон, тёмная комната</t>
         </is>
       </c>
-      <c r="I61" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person frowning at their phone in a dim room, cold blue screen light on their face</t>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person frowning at their phone in a dim room, cold blue screen light on their face</t>
         </is>
       </c>
     </row>
@@ -3325,77 +3461,79 @@
           <t>FEEL</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>day-061.png</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr"/>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>day-061</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>This suit feels expensive.</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Этот костюм на ощупь дорогой.</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>이 정장 원단이 좋아 보여요.</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>Рука ощупывает ткань пиджака в ателье</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a hand feeling the fabric of a suit jacket in a tailor shop, mirror behind</t>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a hand feeling the fabric of a suit jacket in a tailor shop, mirror behind</t>
         </is>
       </c>
     </row>
     <row r="63" ht="44" customHeight="1">
-      <c r="A63" s="11" t="n">
+      <c r="A63" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="12" t="n">
+      <c r="B63" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <t>TURN</t>
         </is>
       </c>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>day-062.png</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr"/>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>day-062</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
         <is>
           <t>I can't believe you've already turned 30.</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr">
+      <c r="G63" s="14" t="inlineStr">
         <is>
           <t>Не верится, что тебе уже тридцать.</t>
         </is>
       </c>
-      <c r="G63" s="13" t="inlineStr">
+      <c r="H63" s="14" t="inlineStr">
         <is>
           <t>벌써 서른이라니 믿기지가 않네요.</t>
         </is>
       </c>
-      <c r="H63" s="13" t="inlineStr">
+      <c r="I63" s="14" t="inlineStr">
         <is>
           <t>Торт со свечами «30», друзья вокруг</t>
         </is>
       </c>
-      <c r="I63" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a birthday cake with 30 candles, friends around the table cheering</t>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a birthday cake with 30 candles, friends around the table cheering</t>
         </is>
       </c>
     </row>
@@ -3411,77 +3549,79 @@
           <t>MOVE</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>day-063.png</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr"/>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>day-063</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>Is it OK if I move the fan away from me?</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Ничего, если я отодвину вентилятор от себя?</t>
         </is>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>선풍기 좀 저쪽으로 돌려도 될까요?</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>Человек отодвигает вентилятор в офисе</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person turning a desk fan away from themselves in an office, colleague nearby</t>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person turning a desk fan away from themselves in an office, colleague nearby</t>
         </is>
       </c>
     </row>
     <row r="65" ht="44" customHeight="1">
-      <c r="A65" s="11" t="n">
+      <c r="A65" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="12" t="n">
+      <c r="B65" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C65" s="13" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
         <is>
           <t>RUN</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
-        <is>
-          <t>day-064.png</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr"/>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>day-064</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>The gift shop is run by nuns.</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr">
+      <c r="G65" s="14" t="inlineStr">
         <is>
           <t>Этим сувенирным магазином управляют монахини.</t>
         </is>
       </c>
-      <c r="G65" s="13" t="inlineStr">
+      <c r="H65" s="14" t="inlineStr">
         <is>
           <t>그 기념품 가게는 수녀님들이 운영해요.</t>
         </is>
       </c>
-      <c r="H65" s="13" t="inlineStr">
+      <c r="I65" s="14" t="inlineStr">
         <is>
           <t>Маленький сувенирный магазин при монастыре, монахини за прилавком</t>
         </is>
       </c>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a small monastery gift shop with nuns behind the counter, shelves of souvenirs</t>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a small monastery gift shop with nuns behind the counter, shelves of souvenirs</t>
         </is>
       </c>
     </row>
@@ -3497,77 +3637,87 @@
           <t>TRY</t>
         </is>
       </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>day-065.png</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>day-065</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>I've never tried acupuncture before.</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>Я никогда не пробовал иглоукалывание.</t>
         </is>
       </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>침 맞아 본 적이 한 번도 없어요.</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="I66" s="8" t="inlineStr">
         <is>
           <t>Кабинет иглотерапии, человек с опаской смотрит на иглы</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: an acupuncture clinic, a first-time patient eyeing the needles nervously</t>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: an acupuncture clinic, a first-time patient eyeing the needles nervously</t>
         </is>
       </c>
     </row>
     <row r="67" ht="44" customHeight="1">
-      <c r="A67" s="11" t="n">
+      <c r="A67" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="12" t="n">
+      <c r="B67" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C67" s="14" t="inlineStr">
         <is>
           <t>STAND</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
-        <is>
-          <t>day-066.png</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>day-066</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
         <is>
           <t>It's so hot I can't stand it.</t>
         </is>
       </c>
-      <c r="F67" s="13" t="inlineStr">
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>Так жарко, что я не выдерживаю.</t>
         </is>
       </c>
-      <c r="G67" s="13" t="inlineStr">
+      <c r="H67" s="14" t="inlineStr">
         <is>
           <t>너무 더워서 못 참겠어요.</t>
         </is>
       </c>
-      <c r="H67" s="13" t="inlineStr">
+      <c r="I67" s="14" t="inlineStr">
         <is>
           <t>Человек обмахивается на раскалённой улице, марево</t>
         </is>
       </c>
-      <c r="I67" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person fanning themselves on a scorching street, heat shimmer, blazing sun</t>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person fanning themselves on a scorching street, heat shimmer, blazing sun</t>
         </is>
       </c>
     </row>
@@ -3583,77 +3733,87 @@
           <t>BREAK</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>day-067.png</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>day-067</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>The handle on my favorite cup broke.</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>У моей любимой чашки отломилась ручка.</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>제일 아끼는 컵 손잡이가 깨졌어요.</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>Чашка без ручки, отломанная ручка рядом</t>
         </is>
       </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a favorite mug on a table with its handle broken off lying beside it, sad mood</t>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a favorite mug on a table with its handle broken off lying beside it, sad mood</t>
         </is>
       </c>
     </row>
     <row r="69" ht="44" customHeight="1">
-      <c r="A69" s="11" t="n">
+      <c r="A69" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="12" t="n">
+      <c r="B69" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C69" s="14" t="inlineStr">
         <is>
           <t>HURT</t>
         </is>
       </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>day-068.png</t>
-        </is>
-      </c>
-      <c r="E69" s="13" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>day-068</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
         <is>
           <t>My tooth hurts when I drink cold water.</t>
         </is>
       </c>
-      <c r="F69" s="13" t="inlineStr">
+      <c r="G69" s="14" t="inlineStr">
         <is>
           <t>У меня болит зуб, когда я пью холодное.</t>
         </is>
       </c>
-      <c r="G69" s="13" t="inlineStr">
+      <c r="H69" s="14" t="inlineStr">
         <is>
           <t>찬물 마시면 이가 시려요.</t>
         </is>
       </c>
-      <c r="H69" s="13" t="inlineStr">
+      <c r="I69" s="14" t="inlineStr">
         <is>
           <t>Человек морщится со стаканом холодной воды</t>
         </is>
       </c>
-      <c r="I69" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person wincing while drinking a glass of ice water, hand on cheek</t>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person wincing while drinking a glass of ice water, hand on cheek</t>
         </is>
       </c>
     </row>
@@ -3669,77 +3829,87 @@
           <t>NOTICE</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>day-069.png</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>day-069</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
         <is>
           <t>I noticed you never eat anything at lunch.</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Я заметил, что ты никогда ничего не ешь в обед.</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>점심때 아무것도 안 드시는 것 같던데요.</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>Коллега замечает нетронутый обед соседа</t>
         </is>
       </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a colleague noticing another's untouched lunch box in an office break room</t>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a colleague noticing another's untouched lunch box in an office break room</t>
         </is>
       </c>
     </row>
     <row r="71" ht="44" customHeight="1">
-      <c r="A71" s="11" t="n">
+      <c r="A71" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="12" t="n">
+      <c r="B71" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C71" s="14" t="inlineStr">
         <is>
           <t>EXPECT</t>
         </is>
       </c>
-      <c r="D71" s="14" t="inlineStr">
-        <is>
-          <t>day-070.png</t>
-        </is>
-      </c>
-      <c r="E71" s="13" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>day-070</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
         <is>
           <t>I expect an answer by tomorrow.</t>
         </is>
       </c>
-      <c r="F71" s="13" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>Жду ответ к завтрашнему дню.</t>
         </is>
       </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="H71" s="14" t="inlineStr">
         <is>
           <t>내일까지는 답변 주셨으면 합니다.</t>
         </is>
       </c>
-      <c r="H71" s="13" t="inlineStr">
+      <c r="I71" s="14" t="inlineStr">
         <is>
           <t>Деловое письмо на экране с дедлайном, календарь</t>
         </is>
       </c>
-      <c r="I71" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a business email on screen with a deadline highlighted, desk calendar showing tomorrow</t>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a business email on screen with a deadline highlighted, desk calendar showing tomorrow</t>
         </is>
       </c>
     </row>
@@ -3755,77 +3925,87 @@
           <t>LOSE</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>day-071.png</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>day-071</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>I just can't believe we lost.</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>Просто не верится, что мы проиграли.</t>
         </is>
       </c>
-      <c r="G72" s="8" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>우리가 졌다는 게 믿기지 않아요.</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>Болельщики в тишине, табло с проигрышем</t>
         </is>
       </c>
-      <c r="I72" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: stunned fans in silence, scoreboard showing a loss, heads in hands</t>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: stunned fans in silence, scoreboard showing a loss, heads in hands</t>
         </is>
       </c>
     </row>
     <row r="73" ht="44" customHeight="1">
-      <c r="A73" s="11" t="n">
+      <c r="A73" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="12" t="n">
+      <c r="B73" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C73" s="14" t="inlineStr">
         <is>
           <t>CATCH</t>
         </is>
       </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>day-072.png</t>
-        </is>
-      </c>
-      <c r="E73" s="13" t="inlineStr">
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>day-072</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
         <is>
           <t>I have to catch the bus at 7 a.m.</t>
         </is>
       </c>
-      <c r="F73" s="13" t="inlineStr">
+      <c r="G73" s="14" t="inlineStr">
         <is>
           <t>Мне надо успеть на автобус в семь утра.</t>
         </is>
       </c>
-      <c r="G73" s="13" t="inlineStr">
+      <c r="H73" s="14" t="inlineStr">
         <is>
           <t>아침 7시 버스를 타야 해요.</t>
         </is>
       </c>
-      <c r="H73" s="13" t="inlineStr">
+      <c r="I73" s="14" t="inlineStr">
         <is>
           <t>Человек бежит к автобусу на рассвете</t>
         </is>
       </c>
-      <c r="I73" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person running toward a bus at an early-morning stop, dawn sky</t>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person running toward a bus at an early-morning stop, dawn sky</t>
         </is>
       </c>
     </row>
@@ -3841,77 +4021,87 @@
           <t>COST</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>day-073.png</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>day-073</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>It costs too much.</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>Это слишком дорого.</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>그건 너무 비싸요.</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>Покупатель смотрит на ценник с удивлением</t>
         </is>
       </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a shopper looking at a price tag with raised eyebrows, upscale store</t>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a shopper looking at a price tag with raised eyebrows, upscale store</t>
         </is>
       </c>
     </row>
     <row r="75" ht="44" customHeight="1">
-      <c r="A75" s="11" t="n">
+      <c r="A75" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B75" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C75" s="13" t="inlineStr">
+      <c r="C75" s="14" t="inlineStr">
         <is>
           <t>OFFER</t>
         </is>
       </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>day-074.png</t>
-        </is>
-      </c>
-      <c r="E75" s="13" t="inlineStr">
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>day-074</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
         <is>
           <t>Twenty thousand won is the most I can offer.</t>
         </is>
       </c>
-      <c r="F75" s="13" t="inlineStr">
+      <c r="G75" s="14" t="inlineStr">
         <is>
           <t>Двадцать тысяч вон — мой максимум.</t>
         </is>
       </c>
-      <c r="G75" s="13" t="inlineStr">
+      <c r="H75" s="14" t="inlineStr">
         <is>
           <t>2만 원이 제가 드릴 수 있는 최대예요.</t>
         </is>
       </c>
-      <c r="H75" s="13" t="inlineStr">
+      <c r="I75" s="14" t="inlineStr">
         <is>
           <t>Торг на рынке, покупатель показывает купюру</t>
         </is>
       </c>
-      <c r="I75" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a market haggling scene, a buyer holding out a banknote, vendor considering</t>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a market haggling scene, a buyer holding out a banknote, vendor considering</t>
         </is>
       </c>
     </row>
@@ -3927,77 +4117,87 @@
           <t>REQUIRE</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>day-075.png</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>day-075</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>Losing weight requires discipline.</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>Похудение требует дисциплины.</t>
         </is>
       </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>살 빼려면 절제가 필요해요.</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>Весы, дневник питания и кроссовки в ряд</t>
         </is>
       </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a scale, a food diary and running shoes lined up neatly, disciplined routine</t>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a scale, a food diary and running shoes lined up neatly, disciplined routine</t>
         </is>
       </c>
     </row>
     <row r="77" ht="44" customHeight="1">
-      <c r="A77" s="11" t="n">
+      <c r="A77" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="12" t="n">
+      <c r="B77" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C77" s="13" t="inlineStr">
+      <c r="C77" s="14" t="inlineStr">
         <is>
           <t>GAIN</t>
         </is>
       </c>
-      <c r="D77" s="14" t="inlineStr">
-        <is>
-          <t>day-076.png</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="inlineStr">
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>day-076</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
         <is>
           <t>I gained a lot of confidence at the English speaking workshop last week.</t>
         </is>
       </c>
-      <c r="F77" s="13" t="inlineStr">
+      <c r="G77" s="14" t="inlineStr">
         <is>
           <t>На воркшопе по английскому на прошлой неделе я сильно прибавил в уверенности.</t>
         </is>
       </c>
-      <c r="G77" s="13" t="inlineStr">
+      <c r="H77" s="14" t="inlineStr">
         <is>
           <t>지난주 영어 회화 워크숍에서 자신감이 많이 붙었어요.</t>
         </is>
       </c>
-      <c r="H77" s="13" t="inlineStr">
+      <c r="I77" s="14" t="inlineStr">
         <is>
           <t>Человек уверенно говорит перед небольшой группой</t>
         </is>
       </c>
-      <c r="I77" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person confidently speaking in front of a small workshop group, others listening</t>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person confidently speaking in front of a small workshop group, others listening</t>
         </is>
       </c>
     </row>
@@ -4013,77 +4213,79 @@
           <t>MENTION</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>day-077.png</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr"/>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>day-077</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>Didn't you mention that you have friends in Osaka?</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>Ты же вроде говорил, что у тебя есть друзья в Осаке?</t>
         </is>
       </c>
-      <c r="G78" s="8" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>오사카에 친구 있다고 하지 않았어요?</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>Двое за столом, один вспоминает разговор, карта Осаки</t>
         </is>
       </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: two people at a table, one recalling something, a map of Osaka between them</t>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: two people at a table, one recalling something, a map of Osaka between them</t>
         </is>
       </c>
     </row>
     <row r="79" ht="44" customHeight="1">
-      <c r="A79" s="11" t="n">
+      <c r="A79" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="12" t="n">
+      <c r="B79" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C79" s="13" t="inlineStr">
+      <c r="C79" s="14" t="inlineStr">
         <is>
           <t>HANDLE</t>
         </is>
       </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>day-078.png</t>
-        </is>
-      </c>
-      <c r="E79" s="13" t="inlineStr">
+      <c r="D79" s="13" t="inlineStr"/>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>day-078</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
         <is>
           <t>I can't handle people like her.</t>
         </is>
       </c>
-      <c r="F79" s="13" t="inlineStr">
+      <c r="G79" s="14" t="inlineStr">
         <is>
           <t>Я не выношу таких людей, как она.</t>
         </is>
       </c>
-      <c r="G79" s="13" t="inlineStr">
+      <c r="H79" s="14" t="inlineStr">
         <is>
           <t>저는 그런 사람 감당이 안 돼요.</t>
         </is>
       </c>
-      <c r="H79" s="13" t="inlineStr">
+      <c r="I79" s="14" t="inlineStr">
         <is>
           <t>Человек устало прикрывает глаза после разговора</t>
         </is>
       </c>
-      <c r="I79" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person pinching the bridge of their nose after a difficult conversation, office</t>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person pinching the bridge of their nose after a difficult conversation, office</t>
         </is>
       </c>
     </row>
@@ -4099,77 +4301,79 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>day-079.png</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr"/>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>day-079</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
         <is>
           <t>Iced coffee sells year-round.</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="G80" s="8" t="inlineStr">
         <is>
           <t>Холодный кофе продаётся круглый год.</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>아이스 커피는 사계절 내내 팔려요.</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>Ледяной кофе на витрине зимой, снег за окном</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: an iced coffee on a cafe counter with snow falling outside the window</t>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: an iced coffee on a cafe counter with snow falling outside the window</t>
         </is>
       </c>
     </row>
     <row r="81" ht="44" customHeight="1">
-      <c r="A81" s="11" t="n">
+      <c r="A81" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="12" t="n">
+      <c r="B81" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C81" s="13" t="inlineStr">
+      <c r="C81" s="14" t="inlineStr">
         <is>
           <t>SUIT</t>
         </is>
       </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>day-080.png</t>
-        </is>
-      </c>
-      <c r="E81" s="13" t="inlineStr">
+      <c r="D81" s="13" t="inlineStr"/>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>day-080</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
         <is>
           <t>Bow ties don't suit me.</t>
         </is>
       </c>
-      <c r="F81" s="13" t="inlineStr">
+      <c r="G81" s="14" t="inlineStr">
         <is>
           <t>Мне не идут бабочки.</t>
         </is>
       </c>
-      <c r="G81" s="13" t="inlineStr">
+      <c r="H81" s="14" t="inlineStr">
         <is>
           <t>저는 나비넥타이가 안 어울려요.</t>
         </is>
       </c>
-      <c r="H81" s="13" t="inlineStr">
+      <c r="I81" s="14" t="inlineStr">
         <is>
           <t>Человек примеряет бабочку перед зеркалом и морщится</t>
         </is>
       </c>
-      <c r="I81" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person trying on a bow tie in front of a mirror and grimacing, shop</t>
+      <c r="J81" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person trying on a bow tie in front of a mirror and grimacing, shop</t>
         </is>
       </c>
     </row>
@@ -4185,77 +4389,79 @@
           <t>MISS</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>day-081.png</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr"/>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>day-081</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
         <is>
           <t>I'm very sorry for missing our meetup yesterday.</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>Прошу прощения, что не пришёл вчера на встречу.</t>
         </is>
       </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>어제 모임에 못 가서 정말 죄송해요.</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="I82" s="8" t="inlineStr">
         <is>
           <t>Пустой стул за столом, друзья без него</t>
         </is>
       </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: an empty chair at a table of friends, one seat conspicuously unfilled</t>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: an empty chair at a table of friends, one seat conspicuously unfilled</t>
         </is>
       </c>
     </row>
     <row r="83" ht="44" customHeight="1">
-      <c r="A83" s="11" t="n">
+      <c r="A83" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="12" t="n">
+      <c r="B83" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C83" s="13" t="inlineStr">
+      <c r="C83" s="14" t="inlineStr">
         <is>
           <t>FINISH ①</t>
         </is>
       </c>
-      <c r="D83" s="14" t="inlineStr">
-        <is>
-          <t>day-082.png</t>
-        </is>
-      </c>
-      <c r="E83" s="13" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr"/>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>day-082</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
         <is>
           <t>The game finished 4-3 in extra innings.</t>
         </is>
       </c>
-      <c r="F83" s="13" t="inlineStr">
+      <c r="G83" s="14" t="inlineStr">
         <is>
           <t>Матч закончился 4:3 в дополнительное время.</t>
         </is>
       </c>
-      <c r="G83" s="13" t="inlineStr">
+      <c r="H83" s="14" t="inlineStr">
         <is>
           <t>경기가 연장에서 4대 3으로 끝났어요.</t>
         </is>
       </c>
-      <c r="H83" s="13" t="inlineStr">
+      <c r="I83" s="14" t="inlineStr">
         <is>
           <t>Табло 4-3, игроки на поле после матча</t>
         </is>
       </c>
-      <c r="I83" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a baseball scoreboard showing 4-3 in extra innings, players walking off the field</t>
+      <c r="J83" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a baseball scoreboard showing 4-3 in extra innings, players walking off the field</t>
         </is>
       </c>
     </row>
@@ -4271,77 +4477,79 @@
           <t>FINISH ②</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>day-083.png</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr"/>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>day-083</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
         <is>
           <t>I can't finish this cake — it's too sweet.</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>Я не смогу доесть этот торт — слишком сладкий.</t>
         </is>
       </c>
-      <c r="G84" s="8" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>이 케이크 너무 달아서 다 못 먹겠어요.</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr">
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>Недоеденный кусок торта, вилка отложена</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a half-eaten slice of very sweet cake with the fork set down beside it</t>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a half-eaten slice of very sweet cake with the fork set down beside it</t>
         </is>
       </c>
     </row>
     <row r="85" ht="44" customHeight="1">
-      <c r="A85" s="11" t="n">
+      <c r="A85" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="12" t="n">
+      <c r="B85" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C85" s="13" t="inlineStr">
+      <c r="C85" s="14" t="inlineStr">
         <is>
           <t>BELONG</t>
         </is>
       </c>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>day-084.png</t>
-        </is>
-      </c>
-      <c r="E85" s="13" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr"/>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>day-084</t>
+        </is>
+      </c>
+      <c r="F85" s="14" t="inlineStr">
         <is>
           <t>These mugs belong in this cupboard.</t>
         </is>
       </c>
-      <c r="F85" s="13" t="inlineStr">
+      <c r="G85" s="14" t="inlineStr">
         <is>
           <t>Эти кружки стоят вот в этом шкафу.</t>
         </is>
       </c>
-      <c r="G85" s="13" t="inlineStr">
+      <c r="H85" s="14" t="inlineStr">
         <is>
           <t>이 컵들은 이 찬장에 놓는 거예요.</t>
         </is>
       </c>
-      <c r="H85" s="13" t="inlineStr">
+      <c r="I85" s="14" t="inlineStr">
         <is>
           <t>Человек ставит кружки на полку шкафа</t>
         </is>
       </c>
-      <c r="I85" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person placing mugs onto a specific kitchen cupboard shelf, organized shelves</t>
+      <c r="J85" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person placing mugs onto a specific kitchen cupboard shelf, organized shelves</t>
         </is>
       </c>
     </row>
@@ -4357,77 +4565,79 @@
           <t>AFFORD</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>day-085.png</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr"/>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>day-085</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>I wish I could afford to buy a place around here.</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>Хотел бы я иметь возможность купить здесь жильё.</t>
         </is>
       </c>
-      <c r="G86" s="8" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>이 동네에 집 살 형편이 됐으면 좋겠어요.</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>Человек смотрит на витрину агентства недвижимости</t>
         </is>
       </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person looking at apartment listings in a real estate agency window, city street</t>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person looking at apartment listings in a real estate agency window, city street</t>
         </is>
       </c>
     </row>
     <row r="87" ht="44" customHeight="1">
-      <c r="A87" s="11" t="n">
+      <c r="A87" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="12" t="n">
+      <c r="B87" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C87" s="13" t="inlineStr">
+      <c r="C87" s="14" t="inlineStr">
         <is>
           <t>GRAB</t>
         </is>
       </c>
-      <c r="D87" s="14" t="inlineStr">
-        <is>
-          <t>day-086.png</t>
-        </is>
-      </c>
-      <c r="E87" s="13" t="inlineStr">
+      <c r="D87" s="13" t="inlineStr"/>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>day-086</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="inlineStr">
         <is>
           <t>Please grab a seat and we'll get started.</t>
         </is>
       </c>
-      <c r="F87" s="13" t="inlineStr">
+      <c r="G87" s="14" t="inlineStr">
         <is>
           <t>Присаживайтесь, и начнём.</t>
         </is>
       </c>
-      <c r="G87" s="13" t="inlineStr">
+      <c r="H87" s="14" t="inlineStr">
         <is>
           <t>자리에 앉으시면 시작하겠습니다.</t>
         </is>
       </c>
-      <c r="H87" s="13" t="inlineStr">
+      <c r="I87" s="14" t="inlineStr">
         <is>
           <t>Спикер приглашает сесть, участники рассаживаются</t>
         </is>
       </c>
-      <c r="I87" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a facilitator gesturing to seats as participants sit down in a workshop room</t>
+      <c r="J87" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a facilitator gesturing to seats as participants sit down in a workshop room</t>
         </is>
       </c>
     </row>
@@ -4443,77 +4653,79 @@
           <t>FIX</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>day-087.png</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr"/>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>day-087</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>I'm not sure if we can fix our marriage.</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>Не уверен, что мы сможем починить наш брак.</t>
         </is>
       </c>
-      <c r="G88" s="8" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>우리 결혼 생활을 되돌릴 수 있을지 모르겠어요.</t>
         </is>
       </c>
-      <c r="H88" s="8" t="inlineStr">
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>Пара сидит на разных концах дивана молча</t>
         </is>
       </c>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a couple sitting silently at opposite ends of a sofa, distance between them</t>
+      <c r="J88" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a couple sitting silently at opposite ends of a sofa, distance between them</t>
         </is>
       </c>
     </row>
     <row r="89" ht="44" customHeight="1">
-      <c r="A89" s="11" t="n">
+      <c r="A89" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="12" t="n">
+      <c r="B89" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C89" s="13" t="inlineStr">
+      <c r="C89" s="14" t="inlineStr">
         <is>
           <t>DESERVE</t>
         </is>
       </c>
-      <c r="D89" s="14" t="inlineStr">
-        <is>
-          <t>day-088.png</t>
-        </is>
-      </c>
-      <c r="E89" s="13" t="inlineStr">
+      <c r="D89" s="13" t="inlineStr"/>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>day-088</t>
+        </is>
+      </c>
+      <c r="F89" s="14" t="inlineStr">
         <is>
           <t>I think they got what they deserve.</t>
         </is>
       </c>
-      <c r="F89" s="13" t="inlineStr">
+      <c r="G89" s="14" t="inlineStr">
         <is>
           <t>Думаю, они получили по заслугам.</t>
         </is>
       </c>
-      <c r="G89" s="13" t="inlineStr">
+      <c r="H89" s="14" t="inlineStr">
         <is>
           <t>걔네는 자업자득이에요.</t>
         </is>
       </c>
-      <c r="H89" s="13" t="inlineStr">
+      <c r="I89" s="14" t="inlineStr">
         <is>
           <t>Человек с лёгкой усмешкой читает новость</t>
         </is>
       </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person reading news on a phone with a knowing half-smile, justice served</t>
+      <c r="J89" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person reading news on a phone with a knowing half-smile, justice served</t>
         </is>
       </c>
     </row>
@@ -4529,77 +4741,79 @@
           <t>MIND</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>day-089.png</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr"/>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>day-089</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>I wouldn't mind staying at this hotel.</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>Я бы не отказался остановиться в этом отеле.</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>이 호텔이면 저는 좋아요.</t>
         </is>
       </c>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Красивый номер отеля, гость одобрительно кивает</t>
         </is>
       </c>
-      <c r="I90" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a stylish hotel room, a guest nodding approvingly from the doorway, suitcase in hand</t>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a stylish hotel room, a guest nodding approvingly from the doorway, suitcase in hand</t>
         </is>
       </c>
     </row>
     <row r="91" ht="44" customHeight="1">
-      <c r="A91" s="11" t="n">
+      <c r="A91" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="12" t="n">
+      <c r="B91" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C91" s="13" t="inlineStr">
+      <c r="C91" s="14" t="inlineStr">
         <is>
           <t>BOOK</t>
         </is>
       </c>
-      <c r="D91" s="14" t="inlineStr">
-        <is>
-          <t>day-090.png</t>
-        </is>
-      </c>
-      <c r="E91" s="13" t="inlineStr">
+      <c r="D91" s="13" t="inlineStr"/>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>day-090</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="inlineStr">
         <is>
           <t>I booked us a room at The Shilla Seoul for our anniversary.</t>
         </is>
       </c>
-      <c r="F91" s="13" t="inlineStr">
+      <c r="G91" s="14" t="inlineStr">
         <is>
           <t>Я забронировал нам номер в The Shilla Seoul на годовщину.</t>
         </is>
       </c>
-      <c r="G91" s="13" t="inlineStr">
+      <c r="H91" s="14" t="inlineStr">
         <is>
           <t>기념일이라 신라호텔에 방 잡았어요.</t>
         </is>
       </c>
-      <c r="H91" s="13" t="inlineStr">
+      <c r="I91" s="14" t="inlineStr">
         <is>
           <t>Пара у стойки регистрации люксового отеля</t>
         </is>
       </c>
-      <c r="I91" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a couple checking in at a luxury hotel front desk, elegant lobby, anniversary mood</t>
+      <c r="J91" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a couple checking in at a luxury hotel front desk, elegant lobby, anniversary mood</t>
         </is>
       </c>
     </row>
@@ -4615,77 +4829,79 @@
           <t>SEEM</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>day-091.png</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr"/>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>day-091</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
         <is>
           <t>You always seem busy with something.</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr">
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>Ты всегда чем-то занят.</t>
         </is>
       </c>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>항상 뭔가 바쁘신 것 같아요.</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>Человек с телефоном, ноутбуком и кофе одновременно</t>
         </is>
       </c>
-      <c r="I92" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person juggling a phone, laptop and coffee at once, perpetually busy</t>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person juggling a phone, laptop and coffee at once, perpetually busy</t>
         </is>
       </c>
     </row>
     <row r="93" ht="44" customHeight="1">
-      <c r="A93" s="11" t="n">
+      <c r="A93" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="12" t="n">
+      <c r="B93" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C93" s="13" t="inlineStr">
+      <c r="C93" s="14" t="inlineStr">
         <is>
           <t>BOTHER ①</t>
         </is>
       </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>day-092.png</t>
-        </is>
-      </c>
-      <c r="E93" s="13" t="inlineStr">
+      <c r="D93" s="13" t="inlineStr"/>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>day-092</t>
+        </is>
+      </c>
+      <c r="F93" s="14" t="inlineStr">
         <is>
           <t>It really bothers me when my laptop is slow.</t>
         </is>
       </c>
-      <c r="F93" s="13" t="inlineStr">
+      <c r="G93" s="14" t="inlineStr">
         <is>
           <t>Меня реально бесит, когда ноутбук тормозит.</t>
         </is>
       </c>
-      <c r="G93" s="13" t="inlineStr">
+      <c r="H93" s="14" t="inlineStr">
         <is>
           <t>노트북 느려지면 진짜 짜증 나요.</t>
         </is>
       </c>
-      <c r="H93" s="13" t="inlineStr">
+      <c r="I93" s="14" t="inlineStr">
         <is>
           <t>Крутящийся индикатор загрузки, человек стучит по столу</t>
         </is>
       </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a spinning loading wheel on a laptop screen, a person drumming fingers impatiently</t>
+      <c r="J93" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a spinning loading wheel on a laptop screen, a person drumming fingers impatiently</t>
         </is>
       </c>
     </row>
@@ -4701,77 +4917,79 @@
           <t>BOTHER ②</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>day-093.png</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr"/>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>day-093</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
         <is>
           <t>He never bothers texting back.</t>
         </is>
       </c>
-      <c r="F94" s="8" t="inlineStr">
+      <c r="G94" s="8" t="inlineStr">
         <is>
           <t>Он никогда не удосуживается ответить на сообщение.</t>
         </is>
       </c>
-      <c r="G94" s="8" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>걔는 답장을 아예 안 해요.</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>Чат без ответа, отправленные сообщения без реакции</t>
         </is>
       </c>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a phone chat with several unanswered sent messages, no reply, disappointed person</t>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a phone chat with several unanswered sent messages, no reply, disappointed person</t>
         </is>
       </c>
     </row>
     <row r="95" ht="44" customHeight="1">
-      <c r="A95" s="11" t="n">
+      <c r="A95" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="12" t="n">
+      <c r="B95" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C95" s="13" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
         <is>
           <t>SPARE</t>
         </is>
       </c>
-      <c r="D95" s="14" t="inlineStr">
-        <is>
-          <t>day-094.png</t>
-        </is>
-      </c>
-      <c r="E95" s="13" t="inlineStr">
+      <c r="D95" s="13" t="inlineStr"/>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>day-094</t>
+        </is>
+      </c>
+      <c r="F95" s="14" t="inlineStr">
         <is>
           <t>Can you spare a moment to help me with something?</t>
         </is>
       </c>
-      <c r="F95" s="13" t="inlineStr">
+      <c r="G95" s="14" t="inlineStr">
         <is>
           <t>Найдётся минутка помочь мне кое с чем?</t>
         </is>
       </c>
-      <c r="G95" s="13" t="inlineStr">
+      <c r="H95" s="14" t="inlineStr">
         <is>
           <t>잠깐 시간 좀 내주실 수 있어요?</t>
         </is>
       </c>
-      <c r="H95" s="13" t="inlineStr">
+      <c r="I95" s="14" t="inlineStr">
         <is>
           <t>Коллега заглядывает в кабинет с просьбой</t>
         </is>
       </c>
-      <c r="I95" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a colleague leaning into a doorway asking for a moment of help, office</t>
+      <c r="J95" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a colleague leaning into a doorway asking for a moment of help, office</t>
         </is>
       </c>
     </row>
@@ -4787,77 +5005,79 @@
           <t>RUIN</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>day-095.png</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr"/>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>day-095</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
         <is>
           <t>Don't eat candy before dinner! You'll ruin your appetite!</t>
         </is>
       </c>
-      <c r="F96" s="8" t="inlineStr">
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>Не ешь конфеты перед ужином! Аппетит перебьёшь!</t>
         </is>
       </c>
-      <c r="G96" s="8" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>저녁 전에 사탕 먹지 마! 입맛 버려!</t>
         </is>
       </c>
-      <c r="H96" s="8" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Родитель забирает конфету у ребёнка перед ужином</t>
         </is>
       </c>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a parent taking a candy from a child's hand before dinner, set table behind</t>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a parent taking a candy from a child's hand before dinner, set table behind</t>
         </is>
       </c>
     </row>
     <row r="97" ht="44" customHeight="1">
-      <c r="A97" s="11" t="n">
+      <c r="A97" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="12" t="n">
+      <c r="B97" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C97" s="13" t="inlineStr">
+      <c r="C97" s="14" t="inlineStr">
         <is>
           <t>OWE</t>
         </is>
       </c>
-      <c r="D97" s="14" t="inlineStr">
-        <is>
-          <t>day-096.png</t>
-        </is>
-      </c>
-      <c r="E97" s="13" t="inlineStr">
+      <c r="D97" s="13" t="inlineStr"/>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>day-096</t>
+        </is>
+      </c>
+      <c r="F97" s="14" t="inlineStr">
         <is>
           <t>I don't owe the bank anything.</t>
         </is>
       </c>
-      <c r="F97" s="13" t="inlineStr">
+      <c r="G97" s="14" t="inlineStr">
         <is>
           <t>Я ничего не должен банку.</t>
         </is>
       </c>
-      <c r="G97" s="13" t="inlineStr">
+      <c r="H97" s="14" t="inlineStr">
         <is>
           <t>저는 은행에 빚이 하나도 없어요.</t>
         </is>
       </c>
-      <c r="H97" s="13" t="inlineStr">
+      <c r="I97" s="14" t="inlineStr">
         <is>
           <t>Человек рвёт справку о кредите, штамп PAID</t>
         </is>
       </c>
-      <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person holding a loan statement stamped PAID, relieved smile, bank counter</t>
+      <c r="J97" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person holding a loan statement stamped PAID, relieved smile, bank counter</t>
         </is>
       </c>
     </row>
@@ -4873,77 +5093,79 @@
           <t>QUIT</t>
         </is>
       </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>day-097.png</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr"/>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>day-097</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
         <is>
           <t>I quit caffeine for a week.</t>
         </is>
       </c>
-      <c r="F98" s="8" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>Я неделю не пил кофеин.</t>
         </is>
       </c>
-      <c r="G98" s="8" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>일주일 동안 카페인 끊었어요.</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr">
+      <c r="I98" s="8" t="inlineStr">
         <is>
           <t>Перечёркнутая чашка кофе, рядом травяной чай</t>
         </is>
       </c>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a crossed-out coffee cup beside a cup of herbal tea, a week marked on a calendar</t>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a crossed-out coffee cup beside a cup of herbal tea, a week marked on a calendar</t>
         </is>
       </c>
     </row>
     <row r="99" ht="44" customHeight="1">
-      <c r="A99" s="11" t="n">
+      <c r="A99" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="12" t="n">
+      <c r="B99" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C99" s="13" t="inlineStr">
+      <c r="C99" s="14" t="inlineStr">
         <is>
           <t>ARRANGE</t>
         </is>
       </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>day-098.png</t>
-        </is>
-      </c>
-      <c r="E99" s="13" t="inlineStr">
+      <c r="D99" s="13" t="inlineStr"/>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>day-098</t>
+        </is>
+      </c>
+      <c r="F99" s="14" t="inlineStr">
         <is>
           <t>I'll arrange for someone to pick you up.</t>
         </is>
       </c>
-      <c r="F99" s="13" t="inlineStr">
+      <c r="G99" s="14" t="inlineStr">
         <is>
           <t>Я организую, чтобы вас встретили.</t>
         </is>
       </c>
-      <c r="G99" s="13" t="inlineStr">
+      <c r="H99" s="14" t="inlineStr">
         <is>
           <t>마중 나갈 사람 준비해 둘게요.</t>
         </is>
       </c>
-      <c r="H99" s="13" t="inlineStr">
+      <c r="I99" s="14" t="inlineStr">
         <is>
           <t>Водитель с табличкой в зале прилёта</t>
         </is>
       </c>
-      <c r="I99" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a driver holding a name sign in an airport arrivals hall, waiting for a guest</t>
+      <c r="J99" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a driver holding a name sign in an airport arrivals hall, waiting for a guest</t>
         </is>
       </c>
     </row>
@@ -4959,82 +5181,84 @@
           <t>SKIP</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>day-099.png</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr"/>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>day-099</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>I never skip leg day.</t>
         </is>
       </c>
-      <c r="F100" s="8" t="inlineStr">
+      <c r="G100" s="8" t="inlineStr">
         <is>
           <t>Я никогда не пропускаю день ног.</t>
         </is>
       </c>
-      <c r="G100" s="8" t="inlineStr">
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>저는 하체 운동 절대 안 빼먹어요.</t>
         </is>
       </c>
-      <c r="H100" s="8" t="inlineStr">
+      <c r="I100" s="8" t="inlineStr">
         <is>
           <t>Человек приседает со штангой в зале</t>
         </is>
       </c>
-      <c r="I100" s="10" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: a person doing barbell squats in a gym, focused, leg day</t>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: a person doing barbell squats in a gym, focused, leg day</t>
         </is>
       </c>
     </row>
     <row r="101" ht="44" customHeight="1">
-      <c r="A101" s="11" t="n">
+      <c r="A101" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="12" t="n">
+      <c r="B101" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C101" s="13" t="inlineStr">
+      <c r="C101" s="14" t="inlineStr">
         <is>
           <t>SPOIL</t>
         </is>
       </c>
-      <c r="D101" s="14" t="inlineStr">
-        <is>
-          <t>day-100.png</t>
-        </is>
-      </c>
-      <c r="E101" s="13" t="inlineStr">
+      <c r="D101" s="13" t="inlineStr"/>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>day-100</t>
+        </is>
+      </c>
+      <c r="F101" s="14" t="inlineStr">
         <is>
           <t>Don't spoil the movie! I haven't seen it yet.</t>
         </is>
       </c>
-      <c r="F101" s="13" t="inlineStr">
+      <c r="G101" s="14" t="inlineStr">
         <is>
           <t>Не спойлери фильм! Я его ещё не смотрел!</t>
         </is>
       </c>
-      <c r="G101" s="13" t="inlineStr">
+      <c r="H101" s="14" t="inlineStr">
         <is>
           <t>영화 스포 하지 마! 아직 안 봤어!</t>
         </is>
       </c>
-      <c r="H101" s="13" t="inlineStr">
+      <c r="I101" s="14" t="inlineStr">
         <is>
           <t>Один зажимает уши, другой рассказывает о фильме</t>
         </is>
       </c>
-      <c r="I101" s="15" t="inlineStr">
-        <is>
-          <t>Flat vector illustration, friendly modern editorial style. Rounded organic shapes, no outlines or very soft outlines, subtle grain texture. Strictly limited palette: warm off-white background #FBF7F1, coral orange #EE6A38, teal #12A39A, deep ink #18262D, sand #E9E1D6. Simple stylized human figures without detailed facial features. No text, no letters, no logos, no watermark. Wide 16:9 composition with generous empty space, subject slightly left of centre. Clean, calm, uncluttered. SCENE: one person covering their ears while another excitedly talks about a movie, cinema lobby</t>
+      <c r="J101" s="16" t="inlineStr">
+        <is>
+          <t>Korean webtoon / anime illustration style, soft cel shading with gentle gradients, warm natural lighting, detailed but uncluttered modern Korean settings. Young adults in their late twenties to thirties, expressive faces, natural poses. Muted natural palette - warm beige, soft grey, dusty blue, terracotta accents. Shallow depth of field, background softly blurred. No text, no captions, no letters, no logos, no watermark, no number badge. Wide horizontal composition, 3:2, subject clearly readable at small size. SCENE: one person covering their ears while another excitedly talks about a movie, cinema lobby</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I101"/>
+  <autoFilter ref="A1:J101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>